--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9994EBF-2749-4DAE-9D5E-875BE3A2C38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC152261-3D25-49E8-8096-EE6FD90CBA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="1170" windowWidth="23610" windowHeight="9420" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="68175" yWindow="4815" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F605"/>
+  <dimension ref="A1:F608"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12498,43 +12498,103 @@
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A604" s="2">
+      <c r="A604">
         <v>7095</v>
       </c>
-      <c r="B604" s="3">
+      <c r="B604">
         <v>6</v>
       </c>
-      <c r="C604" s="3">
+      <c r="C604">
         <v>17</v>
       </c>
-      <c r="D604" s="3">
+      <c r="D604">
         <v>19</v>
       </c>
-      <c r="E604" s="3">
+      <c r="E604">
         <v>39</v>
       </c>
-      <c r="F604" s="3">
+      <c r="F604">
         <v>72</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A605" s="2">
+      <c r="A605">
         <v>7096</v>
       </c>
-      <c r="B605" s="3">
+      <c r="B605">
         <v>10</v>
       </c>
-      <c r="C605" s="3">
+      <c r="C605">
         <v>29</v>
       </c>
-      <c r="D605" s="3">
+      <c r="D605">
         <v>43</v>
       </c>
-      <c r="E605" s="3">
+      <c r="E605">
         <v>47</v>
       </c>
-      <c r="F605" s="3">
+      <c r="F605">
         <v>51</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A606" s="2">
+        <v>7097</v>
+      </c>
+      <c r="B606" s="3">
+        <v>14</v>
+      </c>
+      <c r="C606" s="3">
+        <v>16</v>
+      </c>
+      <c r="D606" s="3">
+        <v>65</v>
+      </c>
+      <c r="E606" s="3">
+        <v>71</v>
+      </c>
+      <c r="F606" s="3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A607" s="2">
+        <v>7098</v>
+      </c>
+      <c r="B607" s="3">
+        <v>4</v>
+      </c>
+      <c r="C607" s="3">
+        <v>17</v>
+      </c>
+      <c r="D607" s="3">
+        <v>21</v>
+      </c>
+      <c r="E607" s="3">
+        <v>38</v>
+      </c>
+      <c r="F607" s="3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A608" s="2">
+        <v>7099</v>
+      </c>
+      <c r="B608" s="3">
+        <v>27</v>
+      </c>
+      <c r="C608" s="3">
+        <v>33</v>
+      </c>
+      <c r="D608" s="3">
+        <v>35</v>
+      </c>
+      <c r="E608" s="3">
+        <v>42</v>
+      </c>
+      <c r="F608" s="3">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -12543,6 +12603,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12710,15 +12779,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12730,6 +12790,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12749,14 +12817,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC152261-3D25-49E8-8096-EE6FD90CBA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B96A69F-3EA3-47CC-8F6D-14A17F14A4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68175" yWindow="4815" windowWidth="18630" windowHeight="9465" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="60300" yWindow="6345" windowWidth="24705" windowHeight="9000" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,13 +103,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F608"/>
+  <dimension ref="A1:F610"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12538,63 +12536,103 @@
       </c>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A606" s="2">
+      <c r="A606">
         <v>7097</v>
       </c>
-      <c r="B606" s="3">
+      <c r="B606">
         <v>14</v>
       </c>
-      <c r="C606" s="3">
+      <c r="C606">
         <v>16</v>
       </c>
-      <c r="D606" s="3">
+      <c r="D606">
         <v>65</v>
       </c>
-      <c r="E606" s="3">
+      <c r="E606">
         <v>71</v>
       </c>
-      <c r="F606" s="3">
+      <c r="F606">
         <v>76</v>
       </c>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A607" s="2">
+      <c r="A607">
         <v>7098</v>
       </c>
-      <c r="B607" s="3">
+      <c r="B607">
         <v>4</v>
       </c>
-      <c r="C607" s="3">
+      <c r="C607">
         <v>17</v>
       </c>
-      <c r="D607" s="3">
+      <c r="D607">
         <v>21</v>
       </c>
-      <c r="E607" s="3">
+      <c r="E607">
         <v>38</v>
       </c>
-      <c r="F607" s="3">
+      <c r="F607">
         <v>47</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A608" s="2">
+      <c r="A608">
         <v>7099</v>
       </c>
-      <c r="B608" s="3">
+      <c r="B608">
         <v>27</v>
       </c>
-      <c r="C608" s="3">
+      <c r="C608">
         <v>33</v>
       </c>
-      <c r="D608" s="3">
+      <c r="D608">
         <v>35</v>
       </c>
-      <c r="E608" s="3">
+      <c r="E608">
         <v>42</v>
       </c>
-      <c r="F608" s="3">
+      <c r="F608">
         <v>59</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A609">
+        <v>7100</v>
+      </c>
+      <c r="B609">
+        <v>27</v>
+      </c>
+      <c r="C609">
+        <v>34</v>
+      </c>
+      <c r="D609">
+        <v>36</v>
+      </c>
+      <c r="E609">
+        <v>48</v>
+      </c>
+      <c r="F609">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A610">
+        <v>7101</v>
+      </c>
+      <c r="B610">
+        <v>32</v>
+      </c>
+      <c r="C610">
+        <v>48</v>
+      </c>
+      <c r="D610">
+        <v>52</v>
+      </c>
+      <c r="E610">
+        <v>62</v>
+      </c>
+      <c r="F610">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -12603,15 +12641,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12779,6 +12808,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -12790,14 +12828,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12817,6 +12847,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B96A69F-3EA3-47CC-8F6D-14A17F14A4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C87E57-0FE0-4A34-B3EB-6C9310D75AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60300" yWindow="6345" windowWidth="24705" windowHeight="9000" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="71880" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F610"/>
+  <dimension ref="A1:F612"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12635,12 +12635,71 @@
         <v>68</v>
       </c>
     </row>
+    <row r="611" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A611">
+        <v>7102</v>
+      </c>
+      <c r="B611">
+        <v>11</v>
+      </c>
+      <c r="C611">
+        <v>14</v>
+      </c>
+      <c r="D611">
+        <v>38</v>
+      </c>
+      <c r="E611">
+        <v>43</v>
+      </c>
+      <c r="F611">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A612">
+        <v>7103</v>
+      </c>
+      <c r="B612">
+        <v>20</v>
+      </c>
+      <c r="C612">
+        <v>25</v>
+      </c>
+      <c r="D612">
+        <v>26</v>
+      </c>
+      <c r="E612">
+        <v>59</v>
+      </c>
+      <c r="F612">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -12808,26 +12867,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12845,23 +12904,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C87E57-0FE0-4A34-B3EB-6C9310D75AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE966C0-C8B2-4B02-BE9B-DB81BECB9379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F612"/>
+  <dimension ref="A1:F613"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12675,12 +12675,41 @@
         <v>68</v>
       </c>
     </row>
+    <row r="613" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A613">
+        <v>7104</v>
+      </c>
+      <c r="B613">
+        <v>7</v>
+      </c>
+      <c r="C613">
+        <v>51</v>
+      </c>
+      <c r="D613">
+        <v>61</v>
+      </c>
+      <c r="E613">
+        <v>66</v>
+      </c>
+      <c r="F613">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -12688,15 +12717,6 @@
     <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12868,20 +12888,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE966C0-C8B2-4B02-BE9B-DB81BECB9379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBF5744-B097-4113-9DA3-00D6C93A7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71835" yWindow="465" windowWidth="14565" windowHeight="13800" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="232" yWindow="1882" windowWidth="26715" windowHeight="11476" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,11 +103,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F613"/>
+  <dimension ref="A1:F622"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12695,21 +12697,192 @@
         <v>75</v>
       </c>
     </row>
+    <row r="614" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A614" s="2">
+        <v>7105</v>
+      </c>
+      <c r="B614" s="3">
+        <v>2</v>
+      </c>
+      <c r="C614" s="3">
+        <v>33</v>
+      </c>
+      <c r="D614" s="3">
+        <v>41</v>
+      </c>
+      <c r="E614" s="3">
+        <v>48</v>
+      </c>
+      <c r="F614" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A615" s="2">
+        <v>7106</v>
+      </c>
+      <c r="B615" s="3">
+        <v>18</v>
+      </c>
+      <c r="C615" s="3">
+        <v>23</v>
+      </c>
+      <c r="D615" s="3">
+        <v>34</v>
+      </c>
+      <c r="E615" s="3">
+        <v>49</v>
+      </c>
+      <c r="F615" s="3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A616" s="2">
+        <v>7107</v>
+      </c>
+      <c r="B616" s="3">
+        <v>33</v>
+      </c>
+      <c r="C616" s="3">
+        <v>36</v>
+      </c>
+      <c r="D616" s="3">
+        <v>49</v>
+      </c>
+      <c r="E616" s="3">
+        <v>61</v>
+      </c>
+      <c r="F616" s="3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A617" s="2">
+        <v>7108</v>
+      </c>
+      <c r="B617" s="3">
+        <v>4</v>
+      </c>
+      <c r="C617" s="3">
+        <v>28</v>
+      </c>
+      <c r="D617" s="3">
+        <v>29</v>
+      </c>
+      <c r="E617" s="3">
+        <v>30</v>
+      </c>
+      <c r="F617" s="3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A618" s="2">
+        <v>7109</v>
+      </c>
+      <c r="B618" s="3">
+        <v>27</v>
+      </c>
+      <c r="C618" s="3">
+        <v>30</v>
+      </c>
+      <c r="D618" s="3">
+        <v>61</v>
+      </c>
+      <c r="E618" s="3">
+        <v>66</v>
+      </c>
+      <c r="F618" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A619" s="2">
+        <v>7110</v>
+      </c>
+      <c r="B619" s="3">
+        <v>9</v>
+      </c>
+      <c r="C619" s="3">
+        <v>14</v>
+      </c>
+      <c r="D619" s="3">
+        <v>54</v>
+      </c>
+      <c r="E619" s="3">
+        <v>57</v>
+      </c>
+      <c r="F619" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A620" s="2">
+        <v>7111</v>
+      </c>
+      <c r="B620" s="3">
+        <v>13</v>
+      </c>
+      <c r="C620" s="3">
+        <v>15</v>
+      </c>
+      <c r="D620" s="3">
+        <v>44</v>
+      </c>
+      <c r="E620" s="3">
+        <v>47</v>
+      </c>
+      <c r="F620" s="3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A621" s="2">
+        <v>7112</v>
+      </c>
+      <c r="B621" s="3">
+        <v>24</v>
+      </c>
+      <c r="C621" s="3">
+        <v>27</v>
+      </c>
+      <c r="D621" s="3">
+        <v>54</v>
+      </c>
+      <c r="E621" s="3">
+        <v>61</v>
+      </c>
+      <c r="F621" s="3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A622" s="2">
+        <v>7113</v>
+      </c>
+      <c r="B622" s="3">
+        <v>1</v>
+      </c>
+      <c r="C622" s="3">
+        <v>32</v>
+      </c>
+      <c r="D622" s="3">
+        <v>57</v>
+      </c>
+      <c r="E622" s="3">
+        <v>78</v>
+      </c>
+      <c r="F622" s="3">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -12717,6 +12890,15 @@
     <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12888,20 +13070,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBF5744-B097-4113-9DA3-00D6C93A7E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3623463E-4269-4221-826F-E86EA75FF94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="232" yWindow="1882" windowWidth="26715" windowHeight="11476" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="67815" yWindow="1470" windowWidth="18705" windowHeight="8280" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,13 +103,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F622"/>
+  <dimension ref="A1:F623"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12698,183 +12696,203 @@
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A614" s="2">
+      <c r="A614">
         <v>7105</v>
       </c>
-      <c r="B614" s="3">
+      <c r="B614">
         <v>2</v>
       </c>
-      <c r="C614" s="3">
+      <c r="C614">
         <v>33</v>
       </c>
-      <c r="D614" s="3">
+      <c r="D614">
         <v>41</v>
       </c>
-      <c r="E614" s="3">
+      <c r="E614">
         <v>48</v>
       </c>
-      <c r="F614" s="3">
+      <c r="F614">
         <v>78</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A615" s="2">
+      <c r="A615">
         <v>7106</v>
       </c>
-      <c r="B615" s="3">
+      <c r="B615">
         <v>18</v>
       </c>
-      <c r="C615" s="3">
+      <c r="C615">
         <v>23</v>
       </c>
-      <c r="D615" s="3">
+      <c r="D615">
         <v>34</v>
       </c>
-      <c r="E615" s="3">
+      <c r="E615">
         <v>49</v>
       </c>
-      <c r="F615" s="3">
+      <c r="F615">
         <v>69</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A616" s="2">
+      <c r="A616">
         <v>7107</v>
       </c>
-      <c r="B616" s="3">
+      <c r="B616">
         <v>33</v>
       </c>
-      <c r="C616" s="3">
+      <c r="C616">
         <v>36</v>
       </c>
-      <c r="D616" s="3">
+      <c r="D616">
         <v>49</v>
       </c>
-      <c r="E616" s="3">
+      <c r="E616">
         <v>61</v>
       </c>
-      <c r="F616" s="3">
+      <c r="F616">
         <v>71</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A617" s="2">
+      <c r="A617">
         <v>7108</v>
       </c>
-      <c r="B617" s="3">
+      <c r="B617">
         <v>4</v>
       </c>
-      <c r="C617" s="3">
+      <c r="C617">
         <v>28</v>
       </c>
-      <c r="D617" s="3">
+      <c r="D617">
         <v>29</v>
       </c>
-      <c r="E617" s="3">
+      <c r="E617">
         <v>30</v>
       </c>
-      <c r="F617" s="3">
+      <c r="F617">
         <v>67</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A618" s="2">
+      <c r="A618">
         <v>7109</v>
       </c>
-      <c r="B618" s="3">
+      <c r="B618">
         <v>27</v>
       </c>
-      <c r="C618" s="3">
+      <c r="C618">
         <v>30</v>
       </c>
-      <c r="D618" s="3">
+      <c r="D618">
         <v>61</v>
       </c>
-      <c r="E618" s="3">
+      <c r="E618">
         <v>66</v>
       </c>
-      <c r="F618" s="3">
+      <c r="F618">
         <v>70</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A619" s="2">
+      <c r="A619">
         <v>7110</v>
       </c>
-      <c r="B619" s="3">
+      <c r="B619">
         <v>9</v>
       </c>
-      <c r="C619" s="3">
+      <c r="C619">
         <v>14</v>
       </c>
-      <c r="D619" s="3">
+      <c r="D619">
         <v>54</v>
       </c>
-      <c r="E619" s="3">
+      <c r="E619">
         <v>57</v>
       </c>
-      <c r="F619" s="3">
+      <c r="F619">
         <v>80</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A620" s="2">
+      <c r="A620">
         <v>7111</v>
       </c>
-      <c r="B620" s="3">
+      <c r="B620">
         <v>13</v>
       </c>
-      <c r="C620" s="3">
+      <c r="C620">
         <v>15</v>
       </c>
-      <c r="D620" s="3">
+      <c r="D620">
         <v>44</v>
       </c>
-      <c r="E620" s="3">
+      <c r="E620">
         <v>47</v>
       </c>
-      <c r="F620" s="3">
+      <c r="F620">
         <v>79</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A621" s="2">
+      <c r="A621">
         <v>7112</v>
       </c>
-      <c r="B621" s="3">
+      <c r="B621">
         <v>24</v>
       </c>
-      <c r="C621" s="3">
+      <c r="C621">
         <v>27</v>
       </c>
-      <c r="D621" s="3">
+      <c r="D621">
         <v>54</v>
       </c>
-      <c r="E621" s="3">
+      <c r="E621">
         <v>61</v>
       </c>
-      <c r="F621" s="3">
+      <c r="F621">
         <v>66</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A622" s="2">
+      <c r="A622">
         <v>7113</v>
       </c>
-      <c r="B622" s="3">
+      <c r="B622">
         <v>1</v>
       </c>
-      <c r="C622" s="3">
+      <c r="C622">
         <v>32</v>
       </c>
-      <c r="D622" s="3">
+      <c r="D622">
         <v>57</v>
       </c>
-      <c r="E622" s="3">
+      <c r="E622">
         <v>78</v>
       </c>
-      <c r="F622" s="3">
+      <c r="F622">
         <v>80</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A623">
+        <v>7114</v>
+      </c>
+      <c r="B623">
+        <v>5</v>
+      </c>
+      <c r="C623">
+        <v>21</v>
+      </c>
+      <c r="D623">
+        <v>43</v>
+      </c>
+      <c r="E623">
+        <v>51</v>
+      </c>
+      <c r="F623">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -12883,25 +12901,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -13069,26 +13068,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <AtualizadoPeloTimerJobEm xmlns="4455b8ba-124f-46d5-aaaa-9813efd83d1e">2025-08-07T04:02:34+00:00</AtualizadoPeloTimerJobEm>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13106,4 +13105,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="4455b8ba-124f-46d5-aaaa-9813efd83d1e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3623463E-4269-4221-826F-E86EA75FF94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0A4418-C134-46FF-A71A-57BCD9316DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67815" yWindow="1470" windowWidth="18705" windowHeight="8280" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57525" yWindow="0" windowWidth="19530" windowHeight="7905" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F623"/>
+  <dimension ref="A1:F637"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -12895,12 +12895,301 @@
         <v>54</v>
       </c>
     </row>
+    <row r="624" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A624">
+        <v>7115</v>
+      </c>
+      <c r="B624">
+        <v>12</v>
+      </c>
+      <c r="C624">
+        <v>43</v>
+      </c>
+      <c r="D624">
+        <v>61</v>
+      </c>
+      <c r="E624">
+        <v>67</v>
+      </c>
+      <c r="F624">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A625">
+        <v>7116</v>
+      </c>
+      <c r="B625">
+        <v>9</v>
+      </c>
+      <c r="C625">
+        <v>16</v>
+      </c>
+      <c r="D625">
+        <v>47</v>
+      </c>
+      <c r="E625">
+        <v>72</v>
+      </c>
+      <c r="F625">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A626">
+        <v>7117</v>
+      </c>
+      <c r="B626">
+        <v>37</v>
+      </c>
+      <c r="C626">
+        <v>40</v>
+      </c>
+      <c r="D626">
+        <v>44</v>
+      </c>
+      <c r="E626">
+        <v>54</v>
+      </c>
+      <c r="F626">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A627">
+        <v>7118</v>
+      </c>
+      <c r="B627">
+        <v>1</v>
+      </c>
+      <c r="C627">
+        <v>3</v>
+      </c>
+      <c r="D627">
+        <v>10</v>
+      </c>
+      <c r="E627">
+        <v>11</v>
+      </c>
+      <c r="F627">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="628" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A628">
+        <v>7119</v>
+      </c>
+      <c r="B628">
+        <v>19</v>
+      </c>
+      <c r="C628">
+        <v>20</v>
+      </c>
+      <c r="D628">
+        <v>24</v>
+      </c>
+      <c r="E628">
+        <v>70</v>
+      </c>
+      <c r="F628">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="629" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A629">
+        <v>7120</v>
+      </c>
+      <c r="B629">
+        <v>12</v>
+      </c>
+      <c r="C629">
+        <v>40</v>
+      </c>
+      <c r="D629">
+        <v>64</v>
+      </c>
+      <c r="E629">
+        <v>66</v>
+      </c>
+      <c r="F629">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="630" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A630">
+        <v>7121</v>
+      </c>
+      <c r="B630">
+        <v>22</v>
+      </c>
+      <c r="C630">
+        <v>23</v>
+      </c>
+      <c r="D630">
+        <v>47</v>
+      </c>
+      <c r="E630">
+        <v>60</v>
+      </c>
+      <c r="F630">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="631" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A631">
+        <v>7122</v>
+      </c>
+      <c r="B631">
+        <v>22</v>
+      </c>
+      <c r="C631">
+        <v>33</v>
+      </c>
+      <c r="D631">
+        <v>35</v>
+      </c>
+      <c r="E631">
+        <v>36</v>
+      </c>
+      <c r="F631">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="632" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A632">
+        <v>7123</v>
+      </c>
+      <c r="B632">
+        <v>14</v>
+      </c>
+      <c r="C632">
+        <v>19</v>
+      </c>
+      <c r="D632">
+        <v>42</v>
+      </c>
+      <c r="E632">
+        <v>53</v>
+      </c>
+      <c r="F632">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A633">
+        <v>7124</v>
+      </c>
+      <c r="B633">
+        <v>22</v>
+      </c>
+      <c r="C633">
+        <v>23</v>
+      </c>
+      <c r="D633">
+        <v>35</v>
+      </c>
+      <c r="E633">
+        <v>54</v>
+      </c>
+      <c r="F633">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A634">
+        <v>7125</v>
+      </c>
+      <c r="B634">
+        <v>38</v>
+      </c>
+      <c r="C634">
+        <v>39</v>
+      </c>
+      <c r="D634">
+        <v>43</v>
+      </c>
+      <c r="E634">
+        <v>51</v>
+      </c>
+      <c r="F634">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A635">
+        <v>7126</v>
+      </c>
+      <c r="B635">
+        <v>21</v>
+      </c>
+      <c r="C635">
+        <v>34</v>
+      </c>
+      <c r="D635">
+        <v>58</v>
+      </c>
+      <c r="E635">
+        <v>69</v>
+      </c>
+      <c r="F635">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A636">
+        <v>7127</v>
+      </c>
+      <c r="B636">
+        <v>1</v>
+      </c>
+      <c r="C636">
+        <v>8</v>
+      </c>
+      <c r="D636">
+        <v>51</v>
+      </c>
+      <c r="E636">
+        <v>57</v>
+      </c>
+      <c r="F636">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A637">
+        <v>7128</v>
+      </c>
+      <c r="B637">
+        <v>10</v>
+      </c>
+      <c r="C637">
+        <v>44</v>
+      </c>
+      <c r="D637">
+        <v>46</v>
+      </c>
+      <c r="E637">
+        <v>70</v>
+      </c>
+      <c r="F637">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -13068,15 +13357,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -13088,6 +13368,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13107,14 +13395,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>

--- a/LoteriasExcel/Quina_edt.xlsx
+++ b/LoteriasExcel/Quina_edt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Dropbox\! 000 ByPass\Pessoal\99_Loterias\0 - Loterias-Inteligentes\LoteriasExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0A4418-C134-46FF-A71A-57BCD9316DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231FCA72-1FE8-4476-B974-1A7179473816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57525" yWindow="0" windowWidth="19530" windowHeight="7905" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
+    <workbookView xWindow="57570" yWindow="0" windowWidth="19845" windowHeight="11865" tabRatio="876" xr2:uid="{2663372B-AA50-4721-AD6B-5F0B8186ACF5}"/>
   </bookViews>
   <sheets>
     <sheet name="QUINA" sheetId="5" r:id="rId1"/>
@@ -103,11 +103,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75F42D8-1A18-4874-B84B-B82C9356D3EB}">
-  <dimension ref="A1:F637"/>
+  <dimension ref="A1:F640"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="9.19921875" customWidth="1"/>
@@ -13175,21 +13177,72 @@
         <v>73</v>
       </c>
     </row>
+    <row r="638" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A638" s="2">
+        <v>7129</v>
+      </c>
+      <c r="B638" s="3">
+        <v>14</v>
+      </c>
+      <c r="C638" s="3">
+        <v>22</v>
+      </c>
+      <c r="D638" s="3">
+        <v>37</v>
+      </c>
+      <c r="E638" s="3">
+        <v>42</v>
+      </c>
+      <c r="F638" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A639" s="2">
+        <v>7130</v>
+      </c>
+      <c r="B639" s="3">
+        <v>4</v>
+      </c>
+      <c r="C639" s="3">
+        <v>16</v>
+      </c>
+      <c r="D639" s="3">
+        <v>61</v>
+      </c>
+      <c r="E639" s="3">
+        <v>69</v>
+      </c>
+      <c r="F639" s="3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A640" s="2">
+        <v>7131</v>
+      </c>
+      <c r="B640" s="3">
+        <v>34</v>
+      </c>
+      <c r="C640" s="3">
+        <v>41</v>
+      </c>
+      <c r="D640" s="3">
+        <v>51</v>
+      </c>
+      <c r="E640" s="3">
+        <v>70</v>
+      </c>
+      <c r="F640" s="3">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C92CDE8829F3C7438DCCB0991C30EAAE" ma:contentTypeVersion="3" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="36cf41eecaf38ba1d849a0c8dd067090">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="3e38fcf2-aa96-4a2c-865b-c3abba01ba51" xmlns:ns3="4455b8ba-124f-46d5-aaaa-9813efd83d1e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="023f68b2d27389a617bf935a3f0e17ad" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -13357,6 +13410,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -13368,14 +13430,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE0BA4B3-539F-4533-9D8B-E25FB604EF71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13395,6 +13449,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BD56D6-0BD8-43E2-A769-DC44C0D1A9D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78031753-5247-4ACF-B096-47D8D4EBED75}">
   <ds:schemaRefs>
